--- a/data/trans_bre/P32C-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; -0,21</t>
+          <t>-1,9; -0,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,22</t>
+          <t>-2,04; 1,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,78</t>
+          <t>-3,66; -0,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,03</t>
+          <t>-0,89; 2,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 307,05</t>
+          <t>-100,0; 460,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,69</t>
+          <t>-2,91; -0,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,68</t>
+          <t>-2,56; -0,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,05</t>
+          <t>-2,47; 0,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,82</t>
+          <t>-1,48; 3,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,65</t>
+          <t>-100,0; 126,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 411,84</t>
+          <t>-80,06; 469,01</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -1,7</t>
+          <t>-5,8; -1,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -1,19</t>
+          <t>-4,0; -1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -0,95</t>
+          <t>-3,55; -0,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,23</t>
+          <t>-1,61; 2,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,06</t>
+          <t>-1,9; 2,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -1,07</t>
+          <t>-4,26; -0,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,41</t>
+          <t>-1,22; 1,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,48</t>
+          <t>-2,09; 0,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 222,46</t>
+          <t>-66,3; 193,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,74</t>
+          <t>-100,0; -14,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,89; 238,95</t>
+          <t>-74,12; 298,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 91,01</t>
+          <t>-86,9; 85,67</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,04</t>
+          <t>-1,78; 0,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -1,02</t>
+          <t>-2,55; -1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; -0,32</t>
+          <t>-1,75; -0,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,82</t>
+          <t>-1,13; 0,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,15; 8,69</t>
+          <t>-81,61; 11,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-96,28; -53,5</t>
+          <t>-96,19; -54,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-86,06; -15,6</t>
+          <t>-88,16; -18,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-69,78; 93,38</t>
+          <t>-72,37; 69,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32C-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32C-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; -0,21</t>
+          <t>-1,68; -0,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,17</t>
+          <t>-2,05; 1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -0,81</t>
+          <t>-3,91; -0,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,07</t>
+          <t>-0,95; 1,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 460,22</t>
+          <t>-100,0; 387,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,7</t>
+          <t>-2,89; -0,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,55</t>
+          <t>-2,55; -0,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,08</t>
+          <t>-2,74; -0,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 3,4</t>
+          <t>-1,36; 2,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 126,57</t>
+          <t>-100,0; 110,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,06; 469,01</t>
+          <t>-77,82; 384,76</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,34%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; -1,73</t>
+          <t>-6,0; -1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -1,18</t>
+          <t>-3,95; -1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,92</t>
+          <t>-3,63; -0,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,55</t>
+          <t>-0,97; 4,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-48,71%</t>
+          <t>-11,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 2,97</t>
+          <t>-1,95; 2,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; -0,85</t>
+          <t>-4,54; -0,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,59</t>
+          <t>-1,31; 1,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,53</t>
+          <t>-1,8; 2,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,3; 193,84</t>
+          <t>-70,32; 186,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,01</t>
+          <t>-100,0; -20,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 298,89</t>
+          <t>-78,26; 307,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 85,67</t>
+          <t>-84,62; 242,46</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-24,41%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,06</t>
+          <t>-1,81; 0,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -1,07</t>
+          <t>-2,52; -1,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; -0,36</t>
+          <t>-1,79; -0,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,65</t>
+          <t>-0,76; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,61; 11,63</t>
+          <t>-78,91; 16,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-96,19; -54,77</t>
+          <t>-100,0; -57,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-88,16; -18,34</t>
+          <t>-88,23; -26,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 69,4</t>
+          <t>-56,96; 148,62</t>
         </is>
       </c>
     </row>
